--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ22"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3136,6 +3136,120 @@
       <c r="AZ22" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/120093072</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137271436</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56881</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Cnephaeus nilssonii</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Svartå Åtorpskorset O, Nrk</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>468261</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6546845</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>03:14</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271436</t>
         </is>
       </c>
     </row>
@@ -3162,6 +3276,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -3144,7 +3144,7 @@
         <v>137271436</v>
       </c>
       <c r="B23" t="n">
-        <v>56881</v>
+        <v>56891</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -3144,7 +3144,7 @@
         <v>137271436</v>
       </c>
       <c r="B23" t="n">
-        <v>56891</v>
+        <v>56892</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 12719-2024 artfynd.xlsx
+++ b/artfynd/A 12719-2024 artfynd.xlsx
@@ -3144,7 +3144,7 @@
         <v>137271436</v>
       </c>
       <c r="B23" t="n">
-        <v>56892</v>
+        <v>56895</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
